--- a/docs/questionnaire/設問一覧.xlsx
+++ b/docs/questionnaire/設問一覧.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -585,7 +585,7 @@
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>今日の乗車についてお答えください。所要5分ほどです。</t>
+          <t>今日の乗車についてお答えください。所要7分ほどです。</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr"/>
@@ -1365,104 +1365,108 @@
       <c r="I28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>①後半</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>S0</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>短文</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>配布カードに書かれたログインID（p01 など）</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr"/>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>①前半</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr"/>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>ページ</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>今日の人数の入れ方について</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>今日ずっと使っていた入れ方について、そのまま思ったとおりにお答えください。</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>①前半</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>単一選択</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>今日の人数の入れ方はどちらでしたか</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>ステッパー方式／テンキー方式／わからない</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="H29" s="8" t="inlineStr">
-        <is>
-          <t>前半と同じIDを入れてください</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>①後半</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>今日の「わからない」ボタンについて</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>今日の1本目と2本目で、画面に1か所だけ違いがありました。</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>ステッパー方式＝「−5」「−1」「＋1」「＋5」のボタンで数を増減させるもの／テンキー方式＝数字のキーを押して直接入力するもの</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>①後半</t>
+          <t>①前半</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>単一選択</t>
+          <t>5段階</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>今日の1本目と2本目で、画面に違いがあったことに気づきましたか</t>
+          <t>今日の入れ方は、全体として答えやすかった</t>
         </is>
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>はっきり気づいた／なんとなく気づいた／気づかなかった</t>
+          <t>まったくそう思わない／とてもそう思う</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
@@ -1474,69 +1478,69 @@
       <c r="I31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>①後半</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>S4</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr"/>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>違いはここです</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>人数を入れる欄のすぐ下に――</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>ボタンごと</t>
-        </is>
-      </c>
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>①前半</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>今日の入れ方は押しやすかった</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr"/>
+      <c r="H32" s="8" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>①後半</t>
+          <t>①前半</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>単一選択</t>
+          <t>5段階</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>「わからない」ボタンがあったほうの乗車を覚えていますか</t>
+          <t>今日の入れ方は素早く答えられた</t>
         </is>
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>1本目／2本目／覚えていない</t>
+          <t>まったくそう思わない／とてもそう思う</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr"/>
@@ -1546,32 +1550,32 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>①後半</t>
+          <t>①前半</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>単一選択</t>
+          <t>5段階</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>ボタンがあったとき、数えきれないときはどうしていましたか</t>
+          <t>今日の入れ方では、自分が思った通りの人数を入力できた</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>ボタンを押した／それらしい数を入れた／空欄で送った／覚えていない</t>
+          <t>まったくそう思わない／とてもそう思う</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr"/>
@@ -1581,32 +1585,32 @@
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>①後半</t>
+          <t>①前半</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
-          <t>4-4</t>
+          <t>2-5</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>単一選択</t>
+          <t>5段階</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>ボタンがなかったとき、数えきれないときはどうしていましたか</t>
+          <t>揺れている車内でも、今日の入れ方は押し間違えにくかった</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>それらしい数を入れた／空欄で送った／クラスだけ選んで送った／覚えていない</t>
+          <t>まったくそう思わない／とてもそう思う</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr"/>
@@ -1616,56 +1620,52 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>①後半</t>
+          <t>①前半</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>4-5</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>単一選択</t>
+          <t>5段階</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>どちらのほうが正直に答えられたと感じますか</t>
+          <t>今日の入れ方は、頭を使う・疲れると感じた</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>ボタンがあった便／ボタンがなかった便／変わらない</t>
+          <t>まったくそう思わない／とてもそう思う</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr"/>
       <c r="H36" s="8" t="inlineStr"/>
-      <c r="I36" s="7" t="inlineStr">
-        <is>
-          <t>ボタン順</t>
-        </is>
-      </c>
+      <c r="I36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>①後半</t>
+          <t>①前半</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>そう思う理由</t>
+          <t>今日の人数の入れ方について、気づいたことがあれば自由にお書きください</t>
         </is>
       </c>
       <c r="F37" s="8" t="inlineStr"/>
@@ -1691,31 +1691,35 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S0</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>4-7</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>5段階</t>
+          <t>短文</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>「わからない」と答えるのに、抵抗や後ろめたさはありましたか</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>まったくなかった／とてもあった</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr"/>
-      <c r="H38" s="8" t="inlineStr"/>
+          <t>配布カードに書かれたログインID（p01 など）</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>前半と同じIDを入れてください</t>
+        </is>
+      </c>
       <c r="I38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1726,38 +1730,50 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S0</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>4-7b</t>
+          <t>0-3</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>段落</t>
+          <t>単一選択</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>（4-7について）よければ理由を教えてください</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="inlineStr"/>
-      <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="8" t="inlineStr"/>
+          <t>今日は何日目ですか</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>1日目／2日目</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>★2日目の方は、最後に追加の質問があります</t>
+        </is>
+      </c>
       <c r="I39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr"/>
@@ -1768,14 +1784,14 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>はじめに</t>
+          <t>今日の「わからない」ボタンについて</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
       <c r="G40" s="5" t="inlineStr"/>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>2日間すべての乗車を終えた方にお答えいただきます。所要5分ほどです。</t>
+          <t>今日の1本目と2本目で、画面に1か所だけ違いがありました。</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr"/>
@@ -1783,30 +1799,34 @@
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>S0</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>0-1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>短文</t>
+          <t>単一選択</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>配布カードに書かれたログインID（p01 など）</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr"/>
+          <t>今日の1本目と2本目で、画面に違いがあったことに気づきましたか</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>はっきり気づいた／なんとなく気づいた／気づかなかった</t>
+        </is>
+      </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
           <t>○</t>
@@ -1816,93 +1836,89 @@
       <c r="I41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>②まとめ</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>S0</t>
-        </is>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>①後半</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr"/>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>違いはここです</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>人数を入れる欄のすぐ下に――</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>ボタンごと</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>①後半</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>単一選択</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>この用紙の版</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>v1／v2／v3／v4</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t>配布カードに書いてあります</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="5" t="inlineStr">
-        <is>
-          <t>②まとめ</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr"/>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>ページ</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>2つの入力方式について</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr"/>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>2日間で、人数の入れ方が日によって違いました。次の2つです。</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr"/>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>「わからない」ボタンがあったほうの乗車を覚えていますか</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>1本目／2本目／覚えていない</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
@@ -1912,153 +1928,137 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>1日目に使ったのはどちらの方式でしたか</t>
+          <t>ボタンがあったとき、数えきれないときはどうしていましたか</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>ステッパー方式／テンキー方式／覚えていない</t>
+          <t>ボタンを押した／それらしい数を入れた／空欄で送った／覚えていない</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr"/>
-      <c r="H44" s="8" t="inlineStr">
-        <is>
-          <t>思い出せる範囲で構いません</t>
-        </is>
-      </c>
+      <c r="H44" s="8" t="inlineStr"/>
       <c r="I44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>4-4</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>5段階</t>
+          <t>単一選択</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>{方式}は押しやすかった</t>
+          <t>ボタンがなかったとき、数えきれないときはどうしていましたか</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>まったくそう思わない／とてもそう思う</t>
+          <t>それらしい数を入れた／空欄で送った／クラスだけ選んで送った／覚えていない</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr"/>
       <c r="H45" s="8" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr">
-        <is>
-          <t>方式ごと</t>
-        </is>
-      </c>
+      <c r="I45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>4-5</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>5段階</t>
+          <t>単一選択</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>{方式}は素早く答えられた</t>
+          <t>どちらのほうが正直に答えられたと感じますか</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>まったくそう思わない／とてもそう思う</t>
+          <t>ボタンがあった便／ボタンがなかった便／変わらない</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr"/>
       <c r="H46" s="8" t="inlineStr"/>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>方式ごと</t>
+          <t>ボタン順</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>5段階</t>
+          <t>段落</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>{方式}では自分が思った通りの人数を入力できた</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="inlineStr">
-        <is>
-          <t>まったくそう思わない／とてもそう思う</t>
-        </is>
-      </c>
+          <t>そう思う理由</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr"/>
       <c r="G47" s="7" t="inlineStr"/>
       <c r="H47" s="8" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr">
-        <is>
-          <t>方式ごと</t>
-        </is>
-      </c>
+      <c r="I47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>4-7</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
@@ -2068,189 +2068,185 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>{方式}は頭を使う・疲れると感じた</t>
+          <t>「わからない」と答えるのに、抵抗や後ろめたさはありましたか</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>まったくそう思わない／とてもそう思う</t>
+          <t>まったくなかった／とてもあった</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr"/>
       <c r="H48" s="8" t="inlineStr"/>
-      <c r="I48" s="7" t="inlineStr">
-        <is>
-          <t>方式ごと</t>
-        </is>
-      </c>
+      <c r="I48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>2-5</t>
+          <t>4-7b</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>単一選択</t>
+          <t>段落</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>2つのうち、答えやすかったのはどちらですか</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="inlineStr">
-        <is>
-          <t>{方式1}／{方式2}／どちらとも言えない</t>
-        </is>
-      </c>
+          <t>（4-7について）よければ理由を教えてください</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="inlineStr"/>
       <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="8" t="inlineStr"/>
       <c r="I49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>②まとめ</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="inlineStr">
-        <is>
-          <t>2-6</t>
-        </is>
-      </c>
-      <c r="D50" s="7" t="inlineStr">
-        <is>
-          <t>段落</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>それはなぜですか</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="inlineStr"/>
-      <c r="G50" s="7" t="inlineStr"/>
-      <c r="H50" s="8" t="inlineStr"/>
-      <c r="I50" s="7" t="inlineStr"/>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>①後半</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr"/>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>ページ</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>★2日目の方だけお答えください</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr"/>
+      <c r="G50" s="5" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>1日目の方は、ここで送信して終わりです。ご協力ありがとうございました。</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>②まとめ</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="C51" s="7" t="inlineStr">
-        <is>
-          <t>2-7</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>単一選択</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>揺れている車内では、どちらが押し間違えにくかったですか</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>{方式1}／{方式2}／どちらとも言えない</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="8" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr"/>
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>①後半</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>アプリ全体の使いやすさ</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr"/>
+      <c r="G51" s="5" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr">
+        <is>
+          <t>2日間を通してのアプリ全体の印象をお答えください。国際的に使われている標準の10項目です。</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>段落</t>
+          <t>5段階</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>それはなぜですか</t>
-        </is>
-      </c>
-      <c r="F52" s="8" t="inlineStr"/>
+          <t>このアプリを頻繁に使いたいと思う</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
       <c r="G52" s="7" t="inlineStr"/>
       <c r="H52" s="8" t="inlineStr"/>
       <c r="I52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>②まとめ</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>①後半</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>S5</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr"/>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>ページ</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>アプリ全体の使いやすさ</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr"/>
-      <c r="G53" s="5" t="inlineStr"/>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>国際的に使われている標準の10項目です。項目の追加・削除・並べ替えはしないでください。</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr"/>
+      <c r="C53" s="7" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>このアプリは不必要に複雑だと思う</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -2260,7 +2256,7 @@
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
@@ -2270,7 +2266,7 @@
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>このアプリを頻繁に使いたいと思う</t>
+          <t>このアプリは簡単に使えると思う</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -2285,7 +2281,7 @@
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -2295,7 +2291,7 @@
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
@@ -2305,7 +2301,7 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>このアプリは不必要に複雑だと思う</t>
+          <t>このアプリを使うには、詳しい人のサポートが必要だと思う</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -2320,7 +2316,7 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -2330,7 +2326,7 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>5-5</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
@@ -2340,7 +2336,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>このアプリは簡単に使えると思う</t>
+          <t>このアプリのさまざまな機能は、うまくまとまっていると思う</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -2355,7 +2351,7 @@
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
@@ -2365,7 +2361,7 @@
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
@@ -2375,7 +2371,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>このアプリを使うには、詳しい人のサポートが必要だと思う</t>
+          <t>このアプリには一貫性のないところが多いと思う</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -2390,7 +2386,7 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -2400,7 +2396,7 @@
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>5-5</t>
+          <t>5-7</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
@@ -2410,7 +2406,7 @@
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>このアプリのさまざまな機能は、うまくまとまっていると思う</t>
+          <t>たいていの人はこのアプリの使い方をすぐに覚えられると思う</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -2425,7 +2421,7 @@
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -2435,7 +2431,7 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>5-8</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -2445,7 +2441,7 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>このアプリには一貫性のないところが多いと思う</t>
+          <t>このアプリはとても使いにくいと思う</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -2460,7 +2456,7 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -2470,7 +2466,7 @@
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>5-7</t>
+          <t>5-9</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
@@ -2480,7 +2476,7 @@
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>たいていの人はこのアプリの使い方をすぐに覚えられると思う</t>
+          <t>このアプリを自信をもって使えた</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -2495,7 +2491,7 @@
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -2505,7 +2501,7 @@
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>5-8</t>
+          <t>5-10</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -2515,7 +2511,7 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>このアプリはとても使いにくいと思う</t>
+          <t>このアプリを使い始める前に、いろいろ覚える必要があった</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -2528,106 +2524,98 @@
       <c r="I61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>②まとめ</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>S5</t>
-        </is>
-      </c>
-      <c r="C62" s="7" t="inlineStr">
-        <is>
-          <t>5-9</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>5段階</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="inlineStr">
-        <is>
-          <t>このアプリを自信をもって使えた</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="inlineStr">
-        <is>
-          <t>まったくそう思わない／とてもそう思う</t>
-        </is>
-      </c>
-      <c r="G62" s="7" t="inlineStr"/>
-      <c r="H62" s="8" t="inlineStr"/>
-      <c r="I62" s="7" t="inlineStr"/>
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>①後半</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr"/>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>最後に、自由にお書きください</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr"/>
+      <c r="G62" s="5" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>5-10</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>5段階</t>
+          <t>段落</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>このアプリを使い始める前に、いろいろ覚える必要があった</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>まったくそう思わない／とてもそう思う</t>
-        </is>
-      </c>
+          <t>人数を答えるとき、いちばん面倒だと感じたことは何ですか</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="inlineStr"/>
       <c r="G63" s="7" t="inlineStr"/>
       <c r="H63" s="8" t="inlineStr"/>
       <c r="I63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="inlineStr">
-        <is>
-          <t>②まとめ</t>
-        </is>
-      </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>①後半</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>S6</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr"/>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>ページ</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>自由にお書きください</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr"/>
-      <c r="G64" s="5" t="inlineStr"/>
-      <c r="H64" s="6" t="inlineStr"/>
-      <c r="I64" s="5" t="inlineStr"/>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>6-2</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>段落</t>
+        </is>
+      </c>
+      <c r="E64" s="8" t="inlineStr">
+        <is>
+          <t>「次に停まるバス停」を選ぶとき、困ったことはありましたか</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr"/>
+      <c r="H64" s="8" t="inlineStr"/>
+      <c r="I64" s="7" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -2637,7 +2625,7 @@
       </c>
       <c r="C65" s="7" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
@@ -2647,7 +2635,7 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>人数を答えるとき、いちばん面倒だと感じたことは何ですか</t>
+          <t>このアプリをこう変えたら答えやすくなる、という案があれば</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr"/>
@@ -2658,7 +2646,7 @@
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>②まとめ</t>
+          <t>①後半</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
@@ -2668,7 +2656,7 @@
       </c>
       <c r="C66" s="7" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
@@ -2678,7 +2666,7 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>「次に停まるバス停」を選ぶとき、困ったことはありましたか</t>
+          <t>実験全体について、気づいたことがあれば</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr"/>
@@ -2686,71 +2674,9 @@
       <c r="H66" s="8" t="inlineStr"/>
       <c r="I66" s="7" t="inlineStr"/>
     </row>
-    <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>②まとめ</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>6-3</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>段落</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>このアプリをこう変えたら答えやすくなる、という案があれば</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr"/>
-      <c r="G67" s="7" t="inlineStr"/>
-      <c r="H67" s="8" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>②まとめ</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>S6</t>
-        </is>
-      </c>
-      <c r="C68" s="7" t="inlineStr">
-        <is>
-          <t>6-4</t>
-        </is>
-      </c>
-      <c r="D68" s="7" t="inlineStr">
-        <is>
-          <t>段落</t>
-        </is>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>実験全体について、気づいたことがあれば</t>
-        </is>
-      </c>
-      <c r="F68" s="8" t="inlineStr"/>
-      <c r="G68" s="7" t="inlineStr"/>
-      <c r="H68" s="8" t="inlineStr"/>
-      <c r="I68" s="7" t="inlineStr"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D6:D68" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D6:D66" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"説明,ページ,短文,段落,単一選択,複数選択,5段階,日付"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/questionnaire/設問一覧.xlsx
+++ b/docs/questionnaire/設問一覧.xlsx
@@ -2712,7 +2712,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>①前半＝解散直後の1枚目／①後半＝それを出してから渡すS4／②まとめ＝2日目の最後</t>
+          <t>①前半＝解散直後の1枚目／①後半＝前半を回収してから渡す2枚目（2日目の方は末尾にSUSが付く）</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>S0 はじめに／S1 普段のこと／S3 今日の答え方／S4 わからないボタン／S2 2方式の比較／S5 使いやすさ／S6 自由記述</t>
+          <t>S0 はじめに／S1 普段のこと／S3 今日の答え方／S2 今日の入れ方の評価／S4 わからないボタン／S5 使いやすさ(SUS)／S6 自由記述</t>
         </is>
       </c>
     </row>

--- a/docs/questionnaire/設問一覧.xlsx
+++ b/docs/questionnaire/設問一覧.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -995,7 +995,7 @@
       <c r="G16" s="4" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>往復が終わったら答えてください（3分ほど）。思ったとおりに選んでください。</t>
+          <t>往復が終わったら答えてください（5分ほど）。思ったとおりに選んでください。</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr"/>
@@ -1520,39 +1520,500 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>2回目</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>2回目</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>ページ</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>アプリ全体について</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>2回使ってみた全体の印象をお答えください。</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>2回目</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>問11</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>このアプリを何度も使いたいと思う</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr"/>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>アプリ全体の使いやすさの点数（SUS）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>2回目</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>問12</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>このアプリは必要以上に複雑だと思う</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr"/>
+      <c r="I32" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>2回目</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>問13</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>このアプリは簡単に使えると思う</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr"/>
+      <c r="I33" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>2回目</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>問14</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>このアプリを使うには、詳しい人の助けが必要だと思う</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr"/>
+      <c r="I34" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>2回目</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>問15</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>このアプリのいろいろな機能は、うまくまとまっていると思う</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr"/>
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>2回目</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>問16</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>このアプリには一貫性のないところが多いと思う</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr"/>
+      <c r="I36" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>2回目</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>問17</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>たいていの人は、このアプリの使い方をすぐ覚えられると思う</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr"/>
+      <c r="I37" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>2回目</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>問18</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>このアプリはとても使いにくいと思う</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr"/>
+      <c r="I38" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>2回目</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>問19</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>このアプリを自信をもって使えた</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr"/>
+      <c r="I39" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>2回目</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>問20</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>このアプリを使う前に、いろいろ覚える必要があった</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr"/>
+      <c r="I40" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>2回目</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>最後に</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>問11</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>問21</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>答えにくかったことがあれば書いてください（なければ「なし」）</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H30" s="7" t="inlineStr"/>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>点数の理由</t>
         </is>
@@ -1560,7 +2021,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D5:D30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D5:D41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"表紙,説明,ページ,ID,短文,段落,単一選択,複数選択,5段階,日付"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/questionnaire/設問一覧.xlsx
+++ b/docs/questionnaire/設問一覧.xlsx
@@ -465,10 +465,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -482,14 +482,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>事後アンケートの設問一覧</t>
+          <t>UI研究のアンケート　設問一覧</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>「設問文」「選択肢」「補足」を直してから python tools/make_forms.py を流すと作り直されます。</t>
+          <t>直したら python tools/make_forms.py（フォームを作るスクリプト）と python tools/make_questionnaire.py（紙の予備）を流す。</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1回目</t>
+          <t>1回目_桃山台</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -559,14 +559,14 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>バスの人数アプリ　1回目のアンケート</t>
+          <t>バスの人数アプリ　1回目　ゆきのアンケート</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
       <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>往復が終わったら答えてください（2分ほど）。思ったとおりに選んでください。</t>
+          <t>桃山台駅で降りたら答えてください（1分ほど）。思ったとおりに選んでください。</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr"/>
@@ -574,7 +574,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>1回目</t>
+          <t>1回目_桃山台</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
@@ -611,36 +611,52 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>1回目</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>1回目_桃山台</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>混み具合</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>今回の往復について</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>ゆきのバスの混み具合</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>空いていた／混んでいた</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr"/>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>その区間の混み具合。同じ区間のクラスの回答・問5 と並べて見る</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>1回目</t>
+          <t>1回目_桃山台</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -650,7 +666,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>問2</t>
+          <t>問3</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -660,12 +676,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>ゆき（吹田駅 → 桃山台駅）のバスの混み具合</t>
+          <t>ゆきのバスで人数を数えきれないことがありましたか</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>空いていた／混んでいた</t>
+          <t>なかった／何度もあった</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -676,14 +692,14 @@
       <c r="H8" s="7" t="inlineStr"/>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>便ごとの混み具合。その便で使った入れ方の点数と並べて見る</t>
+          <t>数えきれないことがどれだけあったか。問2 と並べて、混んでいると数えにくいかを見る</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>1回目</t>
+          <t>1回目_桃山台</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -693,7 +709,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>問3</t>
+          <t>問4</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -703,12 +719,12 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>かえり（桃山台駅 → 吹田駅）のバスの混み具合</t>
+          <t>ゆきのバスで、数えきれないまま、だいたいの人数を入れて送ったことがありましたか</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>空いていた／混んでいた</t>
+          <t>なかった／何度もあった</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -719,24 +735,24 @@
       <c r="H9" s="7" t="inlineStr"/>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>数えられないときに人数を入れてしまったか（記録では分からない）。ボタンがあった回となかった回で比べる</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>1回目</t>
+          <t>1回目_桃山台</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>混み具合</t>
+          <t>入れ方</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>問4</t>
+          <t>問5</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -746,12 +762,12 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>人数を数えきれないことがありましたか</t>
+          <t>ゆきで使った数字キーの答えやすさ</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>なかった／何度もあった</t>
+          <t>答えにくかった／答えやすかった</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -759,44 +775,44 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>0〜9 のキーで人数を打つ画面</t>
+        </is>
+      </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>数えきれないことがどれだけあったか。問2・3 と並べて、混んでいると数えにくいかを見る</t>
+          <t>その区間で使った入れ方の答えやすさ。同じ人の数字キーと＋−ボタンを比べる</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>1回目</t>
+          <t>1回目_桃山台</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>混み具合</t>
+          <t>最後に</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>問5</t>
+          <t>問6</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>5段階</t>
+          <t>段落</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>数えきれないまま、だいたいの人数を入れて送ったことがありましたか</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>なかった／何度もあった</t>
-        </is>
-      </c>
+          <t>答えにくかったことがあれば書いてください（なければ「なし」）</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr"/>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>○</t>
@@ -805,30 +821,30 @@
       <c r="H11" s="7" t="inlineStr"/>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>数えられないときに人数を入れてしまったか（記録では分からない）。ボタンがあった回となかった回で比べる</t>
+          <t>点数の理由</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>1回目</t>
+          <t>1回目_桃山台</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>入れ方</t>
+          <t>回答後</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>説明</t>
+          <t>回答後</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>人数の入れ方について</t>
+          <t>ありがとうございました。かえりのバスでも、バス停を発車するたびに人数を答えてください。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr"/>
@@ -837,126 +853,106 @@
       <c r="I12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>1回目</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>入れ方</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>問6</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>5段階</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>数字キーの答えやすさ</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>答えにくかった／答えやすかった</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>0〜9 のキーで人数を打つ画面</t>
-        </is>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>どちらの入れ方が答えやすいか</t>
-        </is>
-      </c>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>1回目_南口</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>表紙</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr"/>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>表紙</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>バスの人数アプリ　1回目　かえりのアンケート</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>南口に着いたら答えてください（4分ほど）。思ったとおりに選んでください。</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>1回目</t>
+          <t>1回目_南口</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>入れ方</t>
+          <t>はじめに</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>問7</t>
+          <t>問1</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>5段階</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>＋−ボタンの答えやすさ</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>答えにくかった／答えやすかった</t>
-        </is>
-      </c>
+          <t>カードに書いてあるID（例：A）</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr"/>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>−5・−1・＋1・＋5 で人数を合わせる画面</t>
-        </is>
-      </c>
+      <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>アンケートとアプリの記録をつなぐ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>1回目</t>
+          <t>1回目_南口</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>最後に</t>
+          <t>混み具合</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>問8</t>
+          <t>問2</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>段落</t>
+          <t>5段階</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>答えにくかったことがあれば書いてください（なければ「なし」）</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr"/>
+          <t>かえりのバスの混み具合</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>空いていた／混んでいた</t>
+        </is>
+      </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
           <t>○</t>
@@ -965,68 +961,84 @@
       <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>点数の理由</t>
+          <t>その区間の混み具合。同じ区間のクラスの回答・問5 と並べて見る</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>2回目</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>表紙</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>表紙</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>バスの人数アプリ　2回目のアンケート</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>往復が終わったら答えてください（5分ほど）。思ったとおりに選んでください。</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr"/>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>1回目_南口</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>混み具合</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>かえりのバスで人数を数えきれないことがありましたか</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>なかった／何度もあった</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr"/>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>数えきれないことがどれだけあったか。問2 と並べて、混んでいると数えにくいかを見る</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>1回目_南口</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>はじめに</t>
+          <t>混み具合</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>問1</t>
+          <t>問4</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>5段階</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>カードに書いてあるID（例：A）</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr"/>
+          <t>かえりのバスで、数えきれないまま、だいたいの人数を入れて送ったことがありましたか</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>なかった／何度もあった</t>
+        </is>
+      </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>○</t>
@@ -1035,94 +1047,102 @@
       <c r="H17" s="7" t="inlineStr"/>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>アンケートとアプリの記録をつなぐ</t>
+          <t>数えられないときに人数を入れてしまったか（記録では分からない）。ボタンがあった回となかった回で比べる</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>2回目</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>混み具合</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>今回の往復について</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>1回目_南口</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>入れ方</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>かえりで使った＋−ボタンの答えやすさ</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>答えにくかった／答えやすかった</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>−5・−1・＋1・＋5 で人数を合わせる画面</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>その区間で使った入れ方の答えやすさ。同じ人の数字キーと＋−ボタンを比べる</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>2回目</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>混み具合</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>問2</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>5段階</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>ゆき（吹田駅 → 桃山台駅）のバスの混み具合</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>空いていた／混んでいた</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>便ごとの混み具合。その便で使った入れ方の点数と並べて見る</t>
-        </is>
-      </c>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>1回目_南口</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>ページ</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>アプリ全体について</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>今回の往復で使ってみた、アプリ全体の印象をお答えください。</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>1回目_南口</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>混み具合</t>
+          <t>使いやすさ</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>問3</t>
+          <t>問6</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1132,12 +1152,12 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>かえり（桃山台駅 → 吹田駅）のバスの混み具合</t>
+          <t>このアプリを何度も使いたいと思う</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>空いていた／混んでいた</t>
+          <t>まったくそう思わない／とてもそう思う</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -1148,24 +1168,24 @@
       <c r="H20" s="7" t="inlineStr"/>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>アプリ全体の使いやすさの点数（SUS＝使いやすさを測る決まった10問）。ボタンがあった回となかった回で比べる</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>1回目_南口</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>混み具合</t>
+          <t>使いやすさ</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>問4</t>
+          <t>問7</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
@@ -1175,12 +1195,12 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>人数を数えきれないことがありましたか</t>
+          <t>このアプリは必要以上に複雑だと思う</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>なかった／何度もあった</t>
+          <t>まったくそう思わない／とてもそう思う</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
@@ -1191,24 +1211,24 @@
       <c r="H21" s="7" t="inlineStr"/>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>数えきれないことがどれだけあったか。問2・3 と並べて、混んでいると数えにくいかを見る</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>1回目_南口</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>混み具合</t>
+          <t>使いやすさ</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>問5</t>
+          <t>問8</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
@@ -1218,12 +1238,12 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>数えきれないまま、だいたいの人数を入れて送ったことがありましたか</t>
+          <t>このアプリは簡単に使えると思う</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>なかった／何度もあった</t>
+          <t>まったくそう思わない／とてもそう思う</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
@@ -1234,51 +1254,67 @@
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>数えられないときに人数を入れてしまったか（記録では分からない）。ボタンがあった回となかった回で比べる</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>2回目</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>入れ方</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr"/>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>人数の入れ方について</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="4" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>1回目_南口</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>問9</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>このアプリを使うには、詳しい人の助けが必要だと思う</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>1回目_南口</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>入れ方</t>
+          <t>使いやすさ</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>問6</t>
+          <t>問10</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1288,12 +1324,12 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>数字キーの答えやすさ</t>
+          <t>このアプリのいろいろな機能は、うまくまとまっていると思う</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>答えにくかった／答えやすかった</t>
+          <t>まったくそう思わない／とてもそう思う</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
@@ -1301,31 +1337,27 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>0〜9 のキーで人数を打つ画面</t>
-        </is>
-      </c>
+      <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>どちらの入れ方が答えやすいか</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>1回目_南口</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>入れ方</t>
+          <t>使いやすさ</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>問7</t>
+          <t>問11</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1335,12 +1367,12 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>＋−ボタンの答えやすさ</t>
+          <t>このアプリには一貫性のないところが多いと思う</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>答えにくかった／答えやすかった</t>
+          <t>まったくそう思わない／とてもそう思う</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -1348,11 +1380,7 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>−5・−1・＋1・＋5 で人数を合わせる画面</t>
-        </is>
-      </c>
+      <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr">
         <is>
           <t>同上</t>
@@ -1360,65 +1388,77 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>2回目</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>わからない</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>ページ</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>「わからない」ボタンについて</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>1回目と2回目のどちらか一方だけ、人数を入れるところの下に「わからない」ボタンがありました。</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr"/>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>1回目_南口</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>問12</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>たいていの人は、このアプリの使い方をすぐ覚えられると思う</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>1回目_南口</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>わからない</t>
+          <t>使いやすさ</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>問8</t>
+          <t>問13</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>単一選択</t>
+          <t>5段階</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>「わからない」ボタンがあったのは、どちらの回ですか</t>
+          <t>このアプリはとても使いにくいと思う</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>1回目／2回目／覚えていない</t>
+          <t>まったくそう思わない／とてもそう思う</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -1429,39 +1469,39 @@
       <c r="H27" s="7" t="inlineStr"/>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>ボタンに気づいていたか</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>1回目_南口</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>わからない</t>
+          <t>使いやすさ</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>問9</t>
+          <t>問14</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>単一選択</t>
+          <t>5段階</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>人数を答えやすかったのは、どちらの回ですか</t>
+          <t>このアプリを自信をもって使えた</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>1回目／2回目／変わらない</t>
+          <t>まったくそう思わない／とてもそう思う</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -1472,39 +1512,39 @@
       <c r="H28" s="7" t="inlineStr"/>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>ボタンがあると答えやすいか（組から、ボタンがあった回を選んだかを見る）</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>1回目_南口</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>わからない</t>
+          <t>使いやすさ</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>問10</t>
+          <t>問15</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>単一選択</t>
+          <t>5段階</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>数えたとおりの人数を答えられたのは、どちらの回ですか</t>
+          <t>このアプリを使う前に、いろいろ覚える必要があった</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>1回目／2回目／変わらない</t>
+          <t>まったくそう思わない／とてもそう思う</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -1515,158 +1555,134 @@
       <c r="H29" s="7" t="inlineStr"/>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>ボタンがあると正直に答えられるか（同上）</t>
+          <t>同上</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>2回目</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>使いやすさ</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>ページ</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>アプリ全体について</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>2回使ってみた全体の印象をお答えください。</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr"/>
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>1回目_南口</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>最後に</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>問16</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>段落</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>答えにくかったことがあれば書いてください（なければ「なし」）</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr"/>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>点数の理由</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>2回目</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>使いやすさ</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>問11</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>5段階</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>このアプリを何度も使いたいと思う</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>まったくそう思わない／とてもそう思う</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr">
-        <is>
-          <t>アプリ全体の使いやすさの点数（SUS）</t>
-        </is>
-      </c>
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>1回目_南口</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>回答後</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr"/>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>回答後</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>ご協力ありがとうございました。今回はこれで終わりです。</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>2回目</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>使いやすさ</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>問12</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>5段階</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>このアプリは必要以上に複雑だと思う</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>まったくそう思わない／とてもそう思う</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H32" s="7" t="inlineStr"/>
-      <c r="I32" s="7" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>2回目_桃山台</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>表紙</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>表紙</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>バスの人数アプリ　2回目　ゆきのアンケート</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>桃山台駅で降りたら答えてください（1分ほど）。思ったとおりに選んでください。</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>2回目_桃山台</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>使いやすさ</t>
+          <t>はじめに</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>問13</t>
+          <t>問1</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>5段階</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>このアプリは簡単に使えると思う</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>まったくそう思わない／とてもそう思う</t>
-        </is>
-      </c>
+          <t>カードに書いてあるID（例：A）</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr"/>
       <c r="G33" s="6" t="inlineStr">
         <is>
           <t>○</t>
@@ -1675,24 +1691,24 @@
       <c r="H33" s="7" t="inlineStr"/>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>アンケートとアプリの記録をつなぐ</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>2回目_桃山台</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>使いやすさ</t>
+          <t>混み具合</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>問14</t>
+          <t>問2</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1702,12 +1718,12 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>このアプリを使うには、詳しい人の助けが必要だと思う</t>
+          <t>ゆきのバスの混み具合</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>まったくそう思わない／とてもそう思う</t>
+          <t>空いていた／混んでいた</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
@@ -1718,24 +1734,24 @@
       <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>その区間の混み具合。同じ区間のクラスの回答・問5 と並べて見る</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>2回目_桃山台</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>使いやすさ</t>
+          <t>混み具合</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>問15</t>
+          <t>問3</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1745,12 +1761,12 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>このアプリのいろいろな機能は、うまくまとまっていると思う</t>
+          <t>ゆきのバスで人数を数えきれないことがありましたか</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>まったくそう思わない／とてもそう思う</t>
+          <t>なかった／何度もあった</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -1761,24 +1777,24 @@
       <c r="H35" s="7" t="inlineStr"/>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>数えきれないことがどれだけあったか。問2 と並べて、混んでいると数えにくいかを見る</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>2回目_桃山台</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>使いやすさ</t>
+          <t>混み具合</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>問16</t>
+          <t>問4</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1788,12 +1804,12 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>このアプリには一貫性のないところが多いと思う</t>
+          <t>ゆきのバスで、数えきれないまま、だいたいの人数を入れて送ったことがありましたか</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>まったくそう思わない／とてもそう思う</t>
+          <t>なかった／何度もあった</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -1804,24 +1820,24 @@
       <c r="H36" s="7" t="inlineStr"/>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>数えられないときに人数を入れてしまったか（記録では分からない）。ボタンがあった回となかった回で比べる</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>2回目_桃山台</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>使いやすさ</t>
+          <t>入れ方</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>問17</t>
+          <t>問5</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1831,12 +1847,12 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>たいていの人は、このアプリの使い方をすぐ覚えられると思う</t>
+          <t>ゆきで使った＋−ボタンの答えやすさ</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>まったくそう思わない／とてもそう思う</t>
+          <t>答えにくかった／答えやすかった</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -1844,44 +1860,44 @@
           <t>○</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr"/>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>−5・−1・＋1・＋5 で人数を合わせる画面</t>
+        </is>
+      </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>その区間で使った入れ方の答えやすさ。同じ人の数字キーと＋−ボタンを比べる</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>2回目_桃山台</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>使いやすさ</t>
+          <t>最後に</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>問18</t>
+          <t>問6</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>5段階</t>
+          <t>段落</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>このアプリはとても使いにくいと思う</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>まったくそう思わない／とてもそう思う</t>
-        </is>
-      </c>
+          <t>答えにくかったことがあれば書いてください（なければ「なし」）</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr"/>
       <c r="G38" s="6" t="inlineStr">
         <is>
           <t>○</t>
@@ -1890,120 +1906,92 @@
       <c r="H38" s="7" t="inlineStr"/>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>点数の理由</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>2回目</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>使いやすさ</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>問19</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>5段階</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>このアプリを自信をもって使えた</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>まったくそう思わない／とてもそう思う</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>2回目_桃山台</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>回答後</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr"/>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>回答後</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>ありがとうございました。かえりのバスでも、バス停を発車するたびに人数を答えてください。</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>2回目</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>使いやすさ</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>問20</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>5段階</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>このアプリを使う前に、いろいろ覚える必要があった</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>まったくそう思わない／とてもそう思う</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr"/>
-      <c r="I40" s="7" t="inlineStr">
-        <is>
-          <t>同上</t>
-        </is>
-      </c>
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>表紙</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>表紙</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>バスの人数アプリ　2回目　かえりのアンケート</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>南口に着いたら答えてください（5分ほど）。思ったとおりに選んでください。</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2回目</t>
+          <t>2回目_南口</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>最後に</t>
+          <t>はじめに</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>問21</t>
+          <t>問1</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>段落</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>答えにくかったことがあれば書いてください（なければ「なし」）</t>
+          <t>カードに書いてあるID（例：A）</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr"/>
@@ -2015,14 +2003,877 @@
       <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="7" t="inlineStr">
         <is>
+          <t>アンケートとアプリの記録をつなぐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>混み具合</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>問2</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>かえりのバスの混み具合</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>空いていた／混んでいた</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr"/>
+      <c r="I42" s="7" t="inlineStr">
+        <is>
+          <t>その区間の混み具合。同じ区間のクラスの回答・問5 と並べて見る</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>混み具合</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>問3</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>かえりのバスで人数を数えきれないことがありましたか</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>なかった／何度もあった</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr"/>
+      <c r="I43" s="7" t="inlineStr">
+        <is>
+          <t>数えきれないことがどれだけあったか。問2 と並べて、混んでいると数えにくいかを見る</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>混み具合</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>問4</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>かえりのバスで、数えきれないまま、だいたいの人数を入れて送ったことがありましたか</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>なかった／何度もあった</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr"/>
+      <c r="I44" s="7" t="inlineStr">
+        <is>
+          <t>数えられないときに人数を入れてしまったか（記録では分からない）。ボタンがあった回となかった回で比べる</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>入れ方</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>問5</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>かえりで使った数字キーの答えやすさ</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>答えにくかった／答えやすかった</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>0〜9 のキーで人数を打つ画面</t>
+        </is>
+      </c>
+      <c r="I45" s="7" t="inlineStr">
+        <is>
+          <t>その区間で使った入れ方の答えやすさ。同じ人の数字キーと＋−ボタンを比べる</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr"/>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>ページ</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>アプリ全体について</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>今回の往復で使ってみた、アプリ全体の印象をお答えください。</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>問6</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>このアプリを何度も使いたいと思う</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr"/>
+      <c r="I47" s="7" t="inlineStr">
+        <is>
+          <t>アプリ全体の使いやすさの点数（SUS＝使いやすさを測る決まった10問）。ボタンがあった回となかった回で比べる</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>問7</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>このアプリは必要以上に複雑だと思う</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr"/>
+      <c r="I48" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>問8</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>このアプリは簡単に使えると思う</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr"/>
+      <c r="I49" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>問9</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>このアプリを使うには、詳しい人の助けが必要だと思う</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr"/>
+      <c r="I50" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>問10</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>このアプリのいろいろな機能は、うまくまとまっていると思う</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr"/>
+      <c r="I51" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>問11</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>このアプリには一貫性のないところが多いと思う</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr"/>
+      <c r="I52" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>問12</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>たいていの人は、このアプリの使い方をすぐ覚えられると思う</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr"/>
+      <c r="I53" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>問13</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>このアプリはとても使いにくいと思う</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr"/>
+      <c r="I54" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>問14</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>このアプリを自信をもって使えた</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>使いやすさ</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>問15</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>5段階</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>このアプリを使う前に、いろいろ覚える必要があった</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>まったくそう思わない／とてもそう思う</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr"/>
+      <c r="I56" s="7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>わからない</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr"/>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>ページ</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>「わからない」ボタンについて</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>1回目と2回目のどちらか一方だけ、人数を入れるところの下に「わからない」ボタンがありました。</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>わからない</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>問16</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>単一選択</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>「わからない」ボタンがあったのは、どちらの回ですか</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>1回目／2回目／覚えていない</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr">
+        <is>
+          <t>ボタンに気づいていたか</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>わからない</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>問17</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>単一選択</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>人数を答えやすかったのは、どちらの回ですか</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>1回目／2回目／変わらない</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr"/>
+      <c r="I59" s="7" t="inlineStr">
+        <is>
+          <t>ボタンがあると答えやすいか（組から、ボタンがあった回を選んだかを見る）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>わからない</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>問18</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>単一選択</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>数えたとおりの人数を答えられたのは、どちらの回ですか</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>1回目／2回目／変わらない</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr"/>
+      <c r="I60" s="7" t="inlineStr">
+        <is>
+          <t>ボタンがあると正直に答えられるか（同上）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>最後に</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>問19</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>段落</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>答えにくかったことがあれば書いてください（なければ「なし」）</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr"/>
+      <c r="I61" s="7" t="inlineStr">
+        <is>
           <t>点数の理由</t>
         </is>
       </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>2回目_南口</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>回答後</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr"/>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>回答後</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>ご協力ありがとうございました。これで終わりです。</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="5" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D5:D41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"表紙,説明,ページ,ID,短文,段落,単一選択,複数選択,5段階,日付"</formula1>
+    <dataValidation sqref="D5:D62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"表紙,説明,ページ,ID,短文,段落,単一選択,複数選択,5段階,日付,回答後"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
